--- a/docs/Plan_and_Progress/MOSAIC-SoC_Dashboard.xlsx
+++ b/docs/Plan_and_Progress/MOSAIC-SoC_Dashboard.xlsx
@@ -822,7 +822,7 @@
     <col width="28.71" customWidth="1" style="33" min="4" max="4"/>
     <col width="21.57" customWidth="1" style="33" min="5" max="5"/>
     <col width="28.71" customWidth="1" style="33" min="6" max="6"/>
-    <col width="35.86" customWidth="1" style="33" min="7" max="7"/>
+    <col width="46" customWidth="1" style="33" min="7" max="7"/>
     <col width="8.710000000000001" customWidth="1" style="33" min="8" max="26"/>
   </cols>
   <sheetData>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status (2026-08-02)</t>
         </is>
       </c>
       <c r="H11" s="1" t="n"/>
@@ -1223,7 +1223,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1275,9 +1275,9 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>Done (functional; riscv-formal deferred)</t>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H13" s="1" t="n"/>
@@ -1327,9 +1327,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>Done Jun 30 — full-SoC elaboration clean</t>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="1" t="n"/>
@@ -1379,9 +1379,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>Done Jul 10 — all suites green</t>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="1" t="n"/>
@@ -1431,9 +1431,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>Ready — full-SoC sim, sched demo + flash-boot production demo all green; awaiting official GO/NO-GO outcome (Jul 17)</t>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H16" s="1" t="n"/>
@@ -1483,9 +1483,9 @@
           <t>Dry-run</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>Not Started — needs PDK + SRAM macros</t>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>Done Aug 1 - Block A macro DRC/LVS clean (Magic 0, KLayout 0, Netgen "circuits match uniquely", XOR 0, antenna 0, IR drop 104 uV)</t>
         </is>
       </c>
       <c r="H17" s="1" t="n"/>
@@ -1535,9 +1535,9 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>In Progress - macro re-hardened 2026-08-02 with the bug-31 fix: DRC/LVS/XOR/antenna all 0, max-cap 0, max-fanout 1, max-slew 591 vs the library's 4.0 ns. Top-level layout is the MPW integrator's</t>
         </is>
       </c>
       <c r="H18" s="1" t="n"/>
@@ -1587,9 +1587,9 @@
           <t>FINAL</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>Not Started - blocked on re-harden + slew/cap/fanout repair</t>
         </is>
       </c>
       <c r="H19" s="1" t="n"/>
@@ -29106,7 +29106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:Z60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="106" customWidth="1" style="33" min="1" max="1"/>
@@ -29880,7 +29880,7 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>LibreLane flow wired (configs, PDN, SDC); blockers: mosaic_soc_core.sv pin-binding (P-01), SRAM macros (P-03)</t>
+          <t>LibreLane flow wired (configs, PDN, SDC) and now clone-reproducible: run_signoff.sh resolves the filelist from the FuseSoC manifest, zero absolute paths in the checked-in configs. Blockers P-01 (pin-binding) / P-03 (SRAM macros) predate the routed Block A macro and need re-check</t>
         </is>
       </c>
     </row>
@@ -30208,7 +30208,7 @@
       <c r="G28" s="42" t="n"/>
       <c r="H28" s="42" t="inlineStr">
         <is>
-          <t>Await organiser fab dates</t>
+          <t>Await organiser fab dates. Flow side already machine-independent: LibreLane signoff resolves its filelist at run time, no absolute paths in the repo (Aug 3). Container pin still open</t>
         </is>
       </c>
     </row>
@@ -31178,15 +31178,384 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="26.25" customHeight="1" s="33"/>
-    <row r="53" ht="26.25" customHeight="1" s="33"/>
-    <row r="54" ht="26.25" customHeight="1" s="33"/>
-    <row r="55" ht="26.25" customHeight="1" s="33"/>
-    <row r="56" ht="26.25" customHeight="1" s="33"/>
-    <row r="57" ht="26.25" customHeight="1" s="33"/>
-    <row r="58" ht="26.25" customHeight="1" s="33"/>
-    <row r="59" ht="26.25" customHeight="1" s="33"/>
-    <row r="60" ht="26.25" customHeight="1" s="33"/>
+    <row r="52" ht="26.25" customHeight="1" s="33">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t>Selectable platform blocks: soc.dma/debug/plic/spi_mode/multicore_timer/gpio_ao/ao_rv_timer/ao_fast_intr</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F52" s="42" t="inlineStr">
+        <is>
+          <t>Jul 29</t>
+        </is>
+      </c>
+      <c r="G52" s="42" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H52" s="42" t="inlineStr">
+        <is>
+          <t>8 new schema knobs + template gates &amp; tie-offs; 71 tests in test_dma_selection.py; suite 636 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26.25" customHeight="1" s="33">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>GF180 area study: measured reduction 3.903 -&gt; 1.249 mm2 (-68%)</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E53" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F53" s="42" t="inlineStr">
+        <is>
+          <t>Jul 29</t>
+        </is>
+      </c>
+      <c r="G53" s="42" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H53" s="42" t="inlineStr">
+        <is>
+          <t>docs/area_study_gf180_min_soc.md 8c-8g; every step measured (yosys 0.62+slang, tt/25C/5v00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26.25" customHeight="1" s="33">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>Chipathon MPW Block A: 22-pin macro, routed GDS in 1117.5um slot</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E54" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F54" s="42" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G54" s="42" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H54" s="42" t="inlineStr">
+        <is>
+          <t>mosaic_block_a.sv; die 1117.5x1117.5um=1.2488mm2; 0 routing DRC, 0 antenna; setup +20.67ns hold +0.075ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26.25" customHeight="1" s="33">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>GF180 library findings: no latch cell, unattributed SRAM blackboxes, unmapped tristates</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E55" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F55" s="42" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G55" s="42" t="inlineStr">
+        <is>
+          <t>Jul 31</t>
+        </is>
+      </c>
+      <c r="H55" s="42" t="inlineStr">
+        <is>
+          <t>hw/asic/gf180/{tc_clk,gf180_sram_blackbox,sram_wrapper}.sv - icgtp_1 ICG bind, (* blackbox *), bufz_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26.25" customHeight="1" s="33">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>PDN core ring on Metal2/3 conflicts with router layer range</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E56" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F56" s="42" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="G56" s="42" t="inlineStr">
+        <is>
+          <t>Jul 30</t>
+        </is>
+      </c>
+      <c r="H56" s="42" t="inlineStr">
+        <is>
+          <t>All detailed-routing violations were signal-to-VDD shorts on Metal3 along the ring; ring removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26.25" customHeight="1" s="33">
+      <c r="A57" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>DRC + LVS signoff on Block A GDS</t>
+        </is>
+      </c>
+      <c r="C57" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E57" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F57" s="42" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G57" s="42" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="H57" s="42" t="inlineStr">
+        <is>
+          <t>Ran 2026-08-01 with nothing skipped: Magic DRC 0, KLayout DRC 0, Netgen LVS "circuits match uniquely", XOR 0, antenna 0, IR drop 104 uV. Re-hardened Aug 2 with the bug-31 fix, all decks clean again</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26.25" customHeight="1" s="33">
+      <c r="A58" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>Block A power delivery (PSM-0069) unresolved</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E58" s="43" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F58" s="42" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G58" s="42" t="inlineStr">
+        <is>
+          <t>Aug 21</t>
+        </is>
+      </c>
+      <c r="H58" s="42" t="inlineStr">
+        <is>
+          <t>PDN_CORE_RING:false leaves PSM without a power source; IR drop unanalysed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26.25" customHeight="1" s="33">
+      <c r="A59" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>Confirm Block A pin contract with MPW integrator</t>
+        </is>
+      </c>
+      <c r="C59" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E59" s="43" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F59" s="42" t="inlineStr">
+        <is>
+          <t>Aug 1</t>
+        </is>
+      </c>
+      <c r="G59" s="42" t="inlineStr">
+        <is>
+          <t>Aug 7</t>
+        </is>
+      </c>
+      <c r="H59" s="42" t="inlineStr">
+        <is>
+          <t>22 pins; bufz_4 QSPI drive is a placeholder; status_o[6:0] must be bonded (only observability, debug:false)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26.25" customHeight="1" s="33">
+      <c r="A60" s="42" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>LibreLane filelist resolved at run time from the FuseSoC manifest — hardening reproducible on any machine</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>MILOUDIAS</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="E60" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr">
+        <is>
+          <t>Aug 3</t>
+        </is>
+      </c>
+      <c r="G60" s="42" t="inlineStr">
+        <is>
+          <t>Aug 3</t>
+        </is>
+      </c>
+      <c r="H60" s="42" t="inlineStr">
+        <is>
+          <t>flow/librelane/scripts/gen_filelist.py emits VERILOG_FILES/VERILOG_INCLUDE_DIRS from the manifest; 526 absolute build paths out of the two configs (767 -&gt; 241 and 657 -&gt; 131 lines), stale-bundle hazard closed (14 bundles on disk would have hardened the wrong design silently). --verify 507/507 identical; re-run 854 954 um2 / 33 852 cells / 0 check errors, same as signoff. 8 tests in test_librelane_filelist.py; suite 661 green (was 653)</t>
+        </is>
+      </c>
+    </row>
     <row r="61" ht="26.25" customHeight="1" s="33"/>
     <row r="62" ht="26.25" customHeight="1" s="33"/>
     <row r="63" ht="26.25" customHeight="1" s="33"/>
@@ -33823,7 +34192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="70.70999999999999" customWidth="1" style="33" min="1" max="1"/>
@@ -33926,22 +34295,22 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>Week 29 Go/No-Go</t>
+          <t>Resolved Jul 31</t>
         </is>
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>OpenRAM GF180 configs ready (4KB ~0.05mm² fits easily; 32KB needs check); switch to external SRAM / smaller mix if needed</t>
+          <t>Measured: GF180 SRAM macros are area-NEGATIVE below ~512 B (4x sram64x8 = 0.402 mm2 vs ~0.252 mm2 of flip-flops). Frozen part uses a 128 B flip-flop scratchpad, sram_kb: 0</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -33985,17 +34354,17 @@
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>Week 26 (formal)</t>
+          <t>N/A for tapeout</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>FazyRV verified functionally in full-SoC sim; PicoRV32 fallback is now INTEGRATED and sim-verified (D-63) — swap is a one-line config change</t>
+          <t>FazyRV is not in the frozen Block A config (2x SERV). Remains sim-verified in the generator</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -34012,17 +34381,17 @@
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>Week 31 (dry-run)</t>
+          <t>Resolved Aug 1</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>Drop to 25 MHz; 50 MHz was already conservative</t>
+          <t>Frozen part runs at 10 MHz (CLOCK_PERIOD 100) with +20.72 ns setup / +0.055 ns hold worst-corner, TNS 0 at all 9 corners. 50 MHz was dropped deliberately per reviewer advice</t>
         </is>
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Watching</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -34107,11 +34476,141 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26.25" customHeight="1" s="33"/>
-    <row r="13" ht="26.25" customHeight="1" s="33"/>
-    <row r="14" ht="26.25" customHeight="1" s="33"/>
-    <row r="15" ht="26.25" customHeight="1" s="33"/>
-    <row r="16" ht="26.25" customHeight="1" s="33"/>
+    <row r="12" ht="26.25" customHeight="1" s="33">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>Signed-off GDS predates the bug-31 fix</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Resolved Aug 2</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Re-hardened with the fix in place; all decks clean at lower utilization (84.4%) than before</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.25" customHeight="1" s="33">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>Electrical rule violations not covered by any deck</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Before tapeout</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>max-cap 27-&gt;0, max-fanout 411-&gt;1, max-slew 2889-&gt;591 (measured against the library 4.0 ns rather than a tighter blanket default). Residual 591 needs per-net work: CTS_MAX_CAP and bufz_8 pad upsizing were both measured to make it worse</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Open, reduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.25" customHeight="1" s="33">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Hand-modified vendored RTL untested</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Medium (hit)</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>UART FIFOs cut 32-&gt;4 entries for area with no test. Closed by tb/mosaic_soc/run_uart.sh, which measures the depth directly and checks TX against the UART DPI log</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Mitigated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.25" customHeight="1" s="33">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>Timing-annotated GLS unavailable with open tools</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Certain (hit)</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Before tapeout</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>PDK cell models use ifnone on edge-sensitive specify paths (illegal per IEEE 1364-2005 14.2.6); iverilog and CVC both reject, CVC then segfaults on the full netlist. Functional GLS passes; timing coverage rests on STA at 9 corners</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Open - needs commercial simulator</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.25" customHeight="1" s="33">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>Signoff configs pinned to absolute build paths (stale-RTL hardening)</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>High (hit)</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Resolved Aug 3</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Paths resolved from the FuseSoC manifest at run time (gen_filelist.py); the runner stops if the RTL has not been generated instead of reaching for an older bundle. Guarded by test_librelane_filelist.py — the configs may never regain an absolute path</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="26.25" customHeight="1" s="33"/>
     <row r="18" ht="26.25" customHeight="1" s="33"/>
     <row r="19" ht="26.25" customHeight="1" s="33"/>
@@ -35338,9 +35837,21 @@
         </is>
       </c>
       <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>Area reduction 3.903 -&gt; 1.249 mm2 by measurement; 8 selectable platform knobs; Block A 22-pin macro wrapper; first routed GDS in the Chipathon slot</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>DRC/LVS not yet run</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>Run the full signoff decks</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26.25" customHeight="1" s="33">
       <c r="A12" s="44" t="inlineStr">
@@ -35354,9 +35865,21 @@
         </is>
       </c>
       <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>Block A re-hardened with the bug-31 fix: all decks clean, max-cap 27-&gt;0, max-fanout 411-&gt;1, max-slew 2889-&gt;591. RTL frozen + tagged rtl-freeze-blocka-v2. Gate-level simulation on the routed netlist passes (12 399 cycles vs RTL 12 400). UART bring-up test added. LibreLane signoff made reproducible on any machine: the filelist is resolved from the FuseSoC manifest at run time instead of 526 absolute build paths (verify 507/507, re-run identical)</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Timing-annotated GLS blocked: PDK models use illegal ifnone edge paths (IEEE 1364-2005 14.2.6) and CVC segfaults at this scale; 591 max-slew violations remain</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>Per-net slew work; consider a commercial simulator for SDF GLS</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26.25" customHeight="1" s="33">
       <c r="A13" s="44" t="inlineStr">

--- a/docs/Plan_and_Progress/MOSAIC-SoC_Dashboard.xlsx
+++ b/docs/Plan_and_Progress/MOSAIC-SoC_Dashboard.xlsx
@@ -29670,7 +29670,7 @@
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>Functional per-core sims green for all 12 cores (SCI cocotb, all-TITAN SMP, picorv32/snitch/cva6 + rocket/boom/hazard3 wake demos); official arch-test suite not run</t>
+          <t>Functional sims green for 10 of the 14 catalog cores via the full-SoC TB (cv32e20, cv32e40x, fazyrv, serv, picorv32, snitch, cva6, hazard3, rocket, boom); qerv one level down in the cpu_subsystem + LIC TBs. Gaps: ibex is render-only (mosaic_all_cores), cv32e40p/px have no shipped config. Official arch-test suite not run</t>
         </is>
       </c>
     </row>
@@ -29907,7 +29907,7 @@
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F21" s="42" t="inlineStr">
@@ -29917,12 +29917,12 @@
       </c>
       <c r="G21" s="42" t="inlineStr">
         <is>
-          <t>Jul 31</t>
+          <t>Aug 1</t>
         </is>
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
-          <t>Needs P-01..P-03 + GF180 PDK first</t>
+          <t>DRC-clean GDSII achieved 2026-08-01 (Block A macro, all decks 0) but at 10 MHz, not 50: the clock was relaxed to cut timing-repair buffers (0.326 -&gt; 0.114 mm2) and 50 MHz was never re-attempted. Multi-corner STA closes with +20.86 ns setup. Decide whether 50 MHz is still a requirement (dashboard N-07). P-01..P-03 are chip-level and no longer block the macro path</t>
         </is>
       </c>
     </row>
